--- a/artfynd/A 27145-2025 artfynd.xlsx
+++ b/artfynd/A 27145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126744790</v>
       </c>
       <c r="B2" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126744799</v>
       </c>
       <c r="B3" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2025 artfynd.xlsx
+++ b/artfynd/A 27145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126744790</v>
       </c>
       <c r="B2" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126744799</v>
       </c>
       <c r="B3" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2025 artfynd.xlsx
+++ b/artfynd/A 27145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126744790</v>
       </c>
       <c r="B2" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126744799</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27145-2025 artfynd.xlsx
+++ b/artfynd/A 27145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126744790</v>
       </c>
       <c r="B2" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126744799</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126744774</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
